--- a/Tests/Validation/Wheat/data/FAR WAA W20-01a.xlsx
+++ b/Tests/Validation/Wheat/data/FAR WAA W20-01a.xlsx
@@ -1,32 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Observed" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observed" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,16 +48,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -417,126 +430,111 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X123"/>
+  <dimension ref="A1:U123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>SimulationName</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Clock.Today</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Phenology.CurrentStageName</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Wheat.SowingData.Cultivar</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Mgmt</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Potential</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>NDVIModel.Script.NDVI</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>NDVIModel.Script.NDVI.se</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Wheat.AboveGround.Wt</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Wheat.AboveGround.Wt.se</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Density</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Density.se</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Wheat.Grain.Moisture</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Wheat.Grain.WaterContent</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Moisture.se</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Protein</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Protein.se</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Screenings</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Screenings.se</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Wt</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Wt.se</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Wheat.SowingData.Population</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>Wheat.SowingData.Population.se</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>Wheat.Population</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>Wheat.Population.se</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Leaf.StemPopulation</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Leaf.StemPopulation.se</t>
         </is>
@@ -548,33 +546,21 @@
           <t>FAR WAA W20-01aMgmtGrazedCvCutlass</t>
         </is>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="3" t="n">
         <v>44050</v>
       </c>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Cutlass</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>95.45999999999999</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.156453571387808</v>
+      </c>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="n">
-        <v>95.45999999999999</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.156453571387808</v>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
@@ -586,9 +572,6 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -596,31 +579,19 @@
           <t>FAR WAA W20-01aMgmtGrazedCvCutlass</t>
         </is>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Cutlass</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
+      <c r="D3" t="n">
         <v>0.2875</v>
       </c>
-      <c r="H3" t="n">
+      <c r="E3" t="n">
         <v>0.0154784796841723</v>
       </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -634,9 +605,6 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -644,33 +612,21 @@
           <t>FAR WAA W20-01aMgmtGrazedCvCutlass</t>
         </is>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="3" t="n">
         <v>44132</v>
       </c>
       <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Cutlass</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>374.032697649628</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.236878832264959</v>
+      </c>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="n">
-        <v>374.032697649628</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.236878832264959</v>
-      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
@@ -682,9 +638,6 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -692,7 +645,7 @@
           <t>FAR WAA W20-01aMgmtGrazedCvCutlass</t>
         </is>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="3" t="n">
         <v>44161</v>
       </c>
       <c r="C5" t="inlineStr">
@@ -700,27 +653,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Cutlass</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
+      <c r="D5" t="n">
         <v>0.3025</v>
       </c>
-      <c r="H5" t="n">
+      <c r="E5" t="n">
         <v>0.199180613179764</v>
       </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -734,9 +675,6 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -744,7 +682,7 @@
           <t>FAR WAA W20-01aMgmtGrazedCvCutlass</t>
         </is>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C6" t="inlineStr">
@@ -752,29 +690,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Cutlass</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>868.808670302898</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.72066106426118</v>
+      </c>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="n">
-        <v>868.808670302898</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.72066106426118</v>
-      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
@@ -786,9 +712,6 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -796,7 +719,7 @@
           <t>FAR WAA W20-01aMgmtGrazedCvCutlass</t>
         </is>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="3" t="n">
         <v>44182</v>
       </c>
       <c r="C7" t="inlineStr">
@@ -804,59 +727,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Cutlass</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>77.315</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.850573336050453</v>
+      </c>
+      <c r="J7" t="n">
+        <v>13.025</v>
+      </c>
       <c r="K7" t="n">
-        <v>77.315</v>
+        <v>0.110867789130417</v>
       </c>
       <c r="L7" t="n">
-        <v>0.850573336050453</v>
+        <v>10.675</v>
       </c>
       <c r="M7" t="n">
-        <v>13.025</v>
+        <v>0.301039864469807</v>
       </c>
       <c r="N7" t="n">
-        <v>0.110867789130417</v>
+        <v>0.822045603914447</v>
       </c>
       <c r="O7" t="n">
-        <v>10.675</v>
+        <v>0.125641791557319</v>
       </c>
       <c r="P7" t="n">
-        <v>0.301039864469807</v>
+        <v>315.324644985169</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.822045603914447</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.125641791557319</v>
-      </c>
-      <c r="S7" t="n">
-        <v>315.324644985169</v>
-      </c>
-      <c r="T7" t="n">
         <v>0.173655484334526</v>
       </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -864,31 +772,19 @@
           <t>FAR WAA W20-01aMgmtGrazedCvAccroc</t>
         </is>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
+      <c r="D8" t="n">
         <v>0.375</v>
       </c>
-      <c r="H8" t="n">
+      <c r="E8" t="n">
         <v>0.029011491975882</v>
       </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -902,9 +798,6 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -912,33 +805,21 @@
           <t>FAR WAA W20-01aMgmtGrazedCvAccroc</t>
         </is>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="3" t="n">
         <v>44132</v>
       </c>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>902.902237017295</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.608585408610422</v>
+      </c>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="n">
-        <v>902.902237017295</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.608585408610422</v>
-      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
@@ -950,9 +831,6 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -960,7 +838,7 @@
           <t>FAR WAA W20-01aMgmtGrazedCvAccroc</t>
         </is>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="3" t="n">
         <v>44161</v>
       </c>
       <c r="C10" t="inlineStr">
@@ -968,27 +846,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
+      <c r="D10" t="n">
         <v>0.125</v>
       </c>
-      <c r="H10" t="n">
+      <c r="E10" t="n">
         <v>0.00957427107756338</v>
       </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -1002,9 +868,6 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1012,7 +875,7 @@
           <t>FAR WAA W20-01aMgmtGrazedCvAccroc</t>
         </is>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C11" t="inlineStr">
@@ -1020,29 +883,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>933.62243660221</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.95894699437191</v>
+      </c>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="n">
-        <v>933.62243660221</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.95894699437191</v>
-      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
@@ -1054,9 +905,6 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1064,7 +912,7 @@
           <t>FAR WAA W20-01aMgmtGrazedCvAccroc</t>
         </is>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="3" t="n">
         <v>44182</v>
       </c>
       <c r="C12" t="inlineStr">
@@ -1072,59 +920,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>78.69</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.830250966073914</v>
+      </c>
+      <c r="J12" t="n">
+        <v>12.95</v>
+      </c>
       <c r="K12" t="n">
-        <v>78.69</v>
+        <v>0.09574271077563359</v>
       </c>
       <c r="L12" t="n">
-        <v>0.830250966073914</v>
+        <v>10.7</v>
       </c>
       <c r="M12" t="n">
-        <v>12.95</v>
+        <v>0.158113883008419</v>
       </c>
       <c r="N12" t="n">
-        <v>0.09574271077563359</v>
+        <v>1.28926150553002</v>
       </c>
       <c r="O12" t="n">
-        <v>10.7</v>
+        <v>0.281985247881646</v>
       </c>
       <c r="P12" t="n">
-        <v>0.158113883008419</v>
+        <v>294.865369976639</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.28926150553002</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.281985247881646</v>
-      </c>
-      <c r="S12" t="n">
-        <v>294.865369976639</v>
-      </c>
-      <c r="T12" t="n">
         <v>0.328229104609791</v>
       </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1132,33 +965,21 @@
           <t>FAR WAA W20-01aMgmtGrazedCvScepter</t>
         </is>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="3" t="n">
         <v>44050</v>
       </c>
       <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>87.13500000000001</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.0710024119308633</v>
+      </c>
       <c r="H13" t="inlineStr"/>
-      <c r="I13" t="n">
-        <v>87.13500000000001</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.0710024119308633</v>
-      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
@@ -1170,9 +991,6 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1180,31 +998,19 @@
           <t>FAR WAA W20-01aMgmtGrazedCvScepter</t>
         </is>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
+      <c r="D14" t="n">
         <v>0.2425</v>
       </c>
-      <c r="H14" t="n">
+      <c r="E14" t="n">
         <v>0.0075</v>
       </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
@@ -1218,9 +1024,6 @@
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1228,33 +1031,21 @@
           <t>FAR WAA W20-01aMgmtGrazedCvScepter</t>
         </is>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="3" t="n">
         <v>44132</v>
       </c>
       <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>356.364409349476</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.236349807520864</v>
+      </c>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="n">
-        <v>356.364409349476</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.236349807520864</v>
-      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
@@ -1266,9 +1057,6 @@
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1276,7 +1064,7 @@
           <t>FAR WAA W20-01aMgmtGrazedCvScepter</t>
         </is>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="3" t="n">
         <v>44161</v>
       </c>
       <c r="C16" t="inlineStr">
@@ -1284,27 +1072,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
+      <c r="D16" t="n">
         <v>0.1025</v>
       </c>
-      <c r="H16" t="n">
+      <c r="E16" t="n">
         <v>0.00478713553878169</v>
       </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -1318,9 +1094,6 @@
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1328,7 +1101,7 @@
           <t>FAR WAA W20-01aMgmtGrazedCvScepter</t>
         </is>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C17" t="inlineStr">
@@ -1336,29 +1109,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>837.191850103816</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.46579740144812</v>
+      </c>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="n">
-        <v>837.191850103816</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1.46579740144812</v>
-      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
@@ -1370,9 +1131,6 @@
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1380,7 +1138,7 @@
           <t>FAR WAA W20-01aMgmtGrazedCvScepter</t>
         </is>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="3" t="n">
         <v>44182</v>
       </c>
       <c r="C18" t="inlineStr">
@@ -1388,59 +1146,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+      <c r="H18" t="n">
+        <v>79.0625</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.603467411437158</v>
+      </c>
+      <c r="J18" t="n">
+        <v>13.075</v>
+      </c>
       <c r="K18" t="n">
-        <v>79.0625</v>
+        <v>0.103077640640442</v>
       </c>
       <c r="L18" t="n">
-        <v>0.603467411437158</v>
+        <v>10.225</v>
       </c>
       <c r="M18" t="n">
-        <v>13.075</v>
+        <v>0.337577151675485</v>
       </c>
       <c r="N18" t="n">
-        <v>0.103077640640442</v>
+        <v>1.11213886717408</v>
       </c>
       <c r="O18" t="n">
-        <v>10.225</v>
+        <v>0.167460569865782</v>
       </c>
       <c r="P18" t="n">
-        <v>0.337577151675485</v>
+        <v>316.994575250895</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.11213886717408</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.167460569865782</v>
-      </c>
-      <c r="S18" t="n">
-        <v>316.994575250895</v>
-      </c>
-      <c r="T18" t="n">
         <v>0.260056650088186</v>
       </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1448,33 +1191,21 @@
           <t>FAR WAA W20-01aMgmtGrazedCvPascal</t>
         </is>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="3" t="n">
         <v>44050</v>
       </c>
       <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Pascal</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.10412722986808</v>
+      </c>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="n">
-        <v>77.7</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.10412722986808</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
@@ -1486,9 +1217,6 @@
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1496,31 +1224,19 @@
           <t>FAR WAA W20-01aMgmtGrazedCvPascal</t>
         </is>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Pascal</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
+      <c r="D20" t="n">
         <v>0.2525</v>
       </c>
-      <c r="H20" t="n">
+      <c r="E20" t="n">
         <v>0.00478713553878169</v>
       </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
@@ -1534,9 +1250,6 @@
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1544,33 +1257,21 @@
           <t>FAR WAA W20-01aMgmtGrazedCvPascal</t>
         </is>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="3" t="n">
         <v>44132</v>
       </c>
       <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Pascal</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>346.381217675801</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.163400848725564</v>
+      </c>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" t="n">
-        <v>346.381217675801</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.163400848725564</v>
-      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
@@ -1582,9 +1283,6 @@
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1592,7 +1290,7 @@
           <t>FAR WAA W20-01aMgmtGrazedCvPascal</t>
         </is>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="3" t="n">
         <v>44161</v>
       </c>
       <c r="C22" t="inlineStr">
@@ -1600,27 +1298,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Pascal</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
+      <c r="D22" t="n">
         <v>0.11</v>
       </c>
-      <c r="H22" t="n">
+      <c r="E22" t="n">
         <v>0.00408248290463863</v>
       </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
@@ -1634,9 +1320,6 @@
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1644,7 +1327,7 @@
           <t>FAR WAA W20-01aMgmtGrazedCvPascal</t>
         </is>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C23" t="inlineStr">
@@ -1652,29 +1335,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Pascal</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="n">
+        <v>819.02024917711</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.02413878254443</v>
+      </c>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="n">
-        <v>819.02024917711</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2.02413878254443</v>
-      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
@@ -1686,9 +1357,6 @@
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1696,7 +1364,7 @@
           <t>FAR WAA W20-01aMgmtGrazedCvPascal</t>
         </is>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="3" t="n">
         <v>44182</v>
       </c>
       <c r="C24" t="inlineStr">
@@ -1704,59 +1372,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Pascal</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+      <c r="H24" t="n">
+        <v>74.98</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.516220237237299</v>
+      </c>
+      <c r="J24" t="n">
+        <v>12.825</v>
+      </c>
       <c r="K24" t="n">
-        <v>74.98</v>
+        <v>0.143614066163451</v>
       </c>
       <c r="L24" t="n">
-        <v>0.516220237237299</v>
+        <v>11.35</v>
       </c>
       <c r="M24" t="n">
-        <v>12.825</v>
+        <v>0.221735578260835</v>
       </c>
       <c r="N24" t="n">
-        <v>0.143614066163451</v>
+        <v>1.28966191963106</v>
       </c>
       <c r="O24" t="n">
-        <v>11.35</v>
+        <v>0.107187430726232</v>
       </c>
       <c r="P24" t="n">
-        <v>0.221735578260835</v>
+        <v>240.119694464131</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.28966191963106</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0.107187430726232</v>
-      </c>
-      <c r="S24" t="n">
-        <v>240.119694464131</v>
-      </c>
-      <c r="T24" t="n">
         <v>0.0849457299273941</v>
       </c>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1764,31 +1417,19 @@
           <t>FAR WAA W20-01aMgmtGrazedCvMowhawk</t>
         </is>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Mowhawk</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
+      <c r="D25" t="n">
         <v>0.24</v>
       </c>
-      <c r="H25" t="n">
+      <c r="E25" t="n">
         <v>0.00707106781186547</v>
       </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
@@ -1802,9 +1443,6 @@
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1812,33 +1450,21 @@
           <t>FAR WAA W20-01aMgmtGrazedCvMowhawk</t>
         </is>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="3" t="n">
         <v>44132</v>
       </c>
       <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Mowhawk</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="n">
+        <v>957.17044072641</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.833738338438884</v>
+      </c>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="n">
-        <v>957.17044072641</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.833738338438884</v>
-      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
@@ -1850,9 +1476,6 @@
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1860,7 +1483,7 @@
           <t>FAR WAA W20-01aMgmtGrazedCvMowhawk</t>
         </is>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="3" t="n">
         <v>44161</v>
       </c>
       <c r="C27" t="inlineStr">
@@ -1868,27 +1491,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Mowhawk</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
+      <c r="D27" t="n">
         <v>0.11</v>
       </c>
-      <c r="H27" t="n">
+      <c r="E27" t="n">
         <v>0.0168325082306035</v>
       </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
@@ -1902,9 +1513,6 @@
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1912,7 +1520,7 @@
           <t>FAR WAA W20-01aMgmtGrazedCvMowhawk</t>
         </is>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C28" t="inlineStr">
@@ -1920,29 +1528,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Mowhawk</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="n">
+        <v>909.667672772465</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.84212687072176</v>
+      </c>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="n">
-        <v>909.667672772465</v>
-      </c>
-      <c r="J28" t="n">
-        <v>1.84212687072176</v>
-      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
@@ -1954,9 +1550,6 @@
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1964,7 +1557,7 @@
           <t>FAR WAA W20-01aMgmtGrazedCvMowhawk</t>
         </is>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="3" t="n">
         <v>44182</v>
       </c>
       <c r="C29" t="inlineStr">
@@ -1972,59 +1565,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Mowhawk</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="H29" t="n">
+        <v>77.935</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.1120963687259</v>
+      </c>
+      <c r="J29" t="n">
+        <v>12.875</v>
+      </c>
       <c r="K29" t="n">
-        <v>77.935</v>
+        <v>0.125</v>
       </c>
       <c r="L29" t="n">
-        <v>1.1120963687259</v>
+        <v>10.025</v>
       </c>
       <c r="M29" t="n">
-        <v>12.875</v>
+        <v>0.464354390525167</v>
       </c>
       <c r="N29" t="n">
-        <v>0.125</v>
+        <v>1.38434170264052</v>
       </c>
       <c r="O29" t="n">
-        <v>10.025</v>
+        <v>0.250686835689846</v>
       </c>
       <c r="P29" t="n">
-        <v>0.464354390525167</v>
+        <v>313.982710799626</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.38434170264052</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0.250686835689846</v>
-      </c>
-      <c r="S29" t="n">
-        <v>313.982710799626</v>
-      </c>
-      <c r="T29" t="n">
         <v>0.202949283244347</v>
       </c>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2032,31 +1610,19 @@
           <t>FAR WAA W20-01aMgmtGrazedCvAnapurna</t>
         </is>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
+      <c r="D30" t="n">
         <v>0.3425</v>
       </c>
-      <c r="H30" t="n">
+      <c r="E30" t="n">
         <v>0.0225</v>
       </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
@@ -2070,9 +1636,6 @@
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2080,33 +1643,21 @@
           <t>FAR WAA W20-01aMgmtGrazedCvAnapurna</t>
         </is>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="3" t="n">
         <v>44132</v>
       </c>
       <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="n">
+        <v>847.23001179579</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.562925108486485</v>
+      </c>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="n">
-        <v>847.23001179579</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0.562925108486485</v>
-      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
@@ -2118,9 +1669,6 @@
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2128,7 +1676,7 @@
           <t>FAR WAA W20-01aMgmtGrazedCvAnapurna</t>
         </is>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="3" t="n">
         <v>44161</v>
       </c>
       <c r="C32" t="inlineStr">
@@ -2136,27 +1684,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
+      <c r="D32" t="n">
         <v>0.12</v>
       </c>
-      <c r="H32" t="n">
+      <c r="E32" t="n">
         <v>0.00816496580927726</v>
       </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
@@ -2170,9 +1706,6 @@
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2180,7 +1713,7 @@
           <t>FAR WAA W20-01aMgmtGrazedCvAnapurna</t>
         </is>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C33" t="inlineStr">
@@ -2188,29 +1721,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="n">
+        <v>857.4230253063</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.71031116890171</v>
+      </c>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="n">
-        <v>857.4230253063</v>
-      </c>
-      <c r="J33" t="n">
-        <v>1.71031116890171</v>
-      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
@@ -2222,9 +1743,6 @@
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2232,7 +1750,7 @@
           <t>FAR WAA W20-01aMgmtGrazedCvAnapurna</t>
         </is>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="3" t="n">
         <v>44182</v>
       </c>
       <c r="C34" t="inlineStr">
@@ -2240,59 +1758,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="H34" t="n">
+        <v>79.72750000000001</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.978811992502476</v>
+      </c>
+      <c r="J34" t="n">
+        <v>13.125</v>
+      </c>
       <c r="K34" t="n">
-        <v>79.72750000000001</v>
+        <v>0.131497781983829</v>
       </c>
       <c r="L34" t="n">
-        <v>0.978811992502476</v>
+        <v>11.425</v>
       </c>
       <c r="M34" t="n">
-        <v>13.125</v>
+        <v>0.349702254305955</v>
       </c>
       <c r="N34" t="n">
-        <v>0.131497781983829</v>
+        <v>2.0589153823117</v>
       </c>
       <c r="O34" t="n">
-        <v>11.425</v>
+        <v>0.46209250751643</v>
       </c>
       <c r="P34" t="n">
-        <v>0.349702254305955</v>
+        <v>253.774155445311</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.0589153823117</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0.46209250751643</v>
-      </c>
-      <c r="S34" t="n">
-        <v>253.774155445311</v>
-      </c>
-      <c r="T34" t="n">
         <v>0.236732480158472</v>
       </c>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2300,31 +1803,19 @@
           <t>FAR WAA W20-01aMgmtGrazedCvIllabo</t>
         </is>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
+      <c r="D35" t="n">
         <v>0.285</v>
       </c>
-      <c r="H35" t="n">
+      <c r="E35" t="n">
         <v>0.013228756555323</v>
       </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
@@ -2338,9 +1829,6 @@
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2348,33 +1836,21 @@
           <t>FAR WAA W20-01aMgmtGrazedCvIllabo</t>
         </is>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="3" t="n">
         <v>44132</v>
       </c>
       <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>927.394194486904</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.875869997583956</v>
+      </c>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="n">
-        <v>927.394194486904</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0.875869997583956</v>
-      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
@@ -2386,9 +1862,6 @@
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2396,7 +1869,7 @@
           <t>FAR WAA W20-01aMgmtGrazedCvIllabo</t>
         </is>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="3" t="n">
         <v>44161</v>
       </c>
       <c r="C37" t="inlineStr">
@@ -2404,27 +1877,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
+      <c r="D37" t="n">
         <v>0.245</v>
       </c>
-      <c r="H37" t="n">
+      <c r="E37" t="n">
         <v>0.151684980579269</v>
       </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
@@ -2438,9 +1899,6 @@
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2448,7 +1906,7 @@
           <t>FAR WAA W20-01aMgmtGrazedCvIllabo</t>
         </is>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C38" t="inlineStr">
@@ -2456,29 +1914,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="n">
+        <v>903.454229458956</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2.06420204004463</v>
+      </c>
       <c r="H38" t="inlineStr"/>
-      <c r="I38" t="n">
-        <v>903.454229458956</v>
-      </c>
-      <c r="J38" t="n">
-        <v>2.06420204004463</v>
-      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
@@ -2490,9 +1936,6 @@
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2500,7 +1943,7 @@
           <t>FAR WAA W20-01aMgmtGrazedCvIllabo</t>
         </is>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="3" t="n">
         <v>44182</v>
       </c>
       <c r="C39" t="inlineStr">
@@ -2508,59 +1951,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+      <c r="H39" t="n">
+        <v>73.4375</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.615377594110588</v>
+      </c>
+      <c r="J39" t="n">
+        <v>13</v>
+      </c>
       <c r="K39" t="n">
-        <v>73.4375</v>
+        <v>0.09128709291752719</v>
       </c>
       <c r="L39" t="n">
-        <v>0.615377594110588</v>
+        <v>10.1</v>
       </c>
       <c r="M39" t="n">
-        <v>13</v>
+        <v>0.212132034355964</v>
       </c>
       <c r="N39" t="n">
-        <v>0.09128709291752719</v>
+        <v>1.26441807668644</v>
       </c>
       <c r="O39" t="n">
-        <v>10.1</v>
+        <v>0.342410691159044</v>
       </c>
       <c r="P39" t="n">
-        <v>0.212132034355964</v>
+        <v>259.962464236029</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.26441807668644</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0.342410691159044</v>
-      </c>
-      <c r="S39" t="n">
-        <v>259.962464236029</v>
-      </c>
-      <c r="T39" t="n">
         <v>0.0566402063971571</v>
       </c>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2568,31 +1996,19 @@
           <t>FAR WAA W20-01aMgmtHigh InputCvAccroc</t>
         </is>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
+      <c r="D40" t="n">
         <v>0.4325</v>
       </c>
-      <c r="H40" t="n">
+      <c r="E40" t="n">
         <v>0.0131497781983829</v>
       </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
@@ -2606,9 +2022,6 @@
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2616,33 +2029,21 @@
           <t>FAR WAA W20-01aMgmtHigh InputCvAccroc</t>
         </is>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="3" t="n">
         <v>44132</v>
       </c>
       <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="n">
+        <v>925.00251572327</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1.01811509200389</v>
+      </c>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="n">
-        <v>925.00251572327</v>
-      </c>
-      <c r="J41" t="n">
-        <v>1.01811509200389</v>
-      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
@@ -2654,9 +2055,6 @@
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
-      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2664,7 +2062,7 @@
           <t>FAR WAA W20-01aMgmtHigh InputCvAccroc</t>
         </is>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="3" t="n">
         <v>44161</v>
       </c>
       <c r="C42" t="inlineStr">
@@ -2672,27 +2070,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
+      <c r="D42" t="n">
         <v>0.115</v>
       </c>
-      <c r="H42" t="n">
+      <c r="E42" t="n">
         <v>0.00957427107756338</v>
       </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
@@ -2706,9 +2092,6 @@
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2716,7 +2099,7 @@
           <t>FAR WAA W20-01aMgmtHigh InputCvAccroc</t>
         </is>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C43" t="inlineStr">
@@ -2724,29 +2107,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="n">
+        <v>763.334826287388</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1.73836686560917</v>
+      </c>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" t="n">
-        <v>763.334826287388</v>
-      </c>
-      <c r="J43" t="n">
-        <v>1.73836686560917</v>
-      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
@@ -2758,9 +2129,6 @@
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2768,7 +2136,7 @@
           <t>FAR WAA W20-01aMgmtHigh InputCvAccroc</t>
         </is>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="3" t="n">
         <v>44182</v>
       </c>
       <c r="C44" t="inlineStr">
@@ -2776,59 +2144,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+      <c r="H44" t="n">
+        <v>77.36750000000001</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1.79015071525649</v>
+      </c>
+      <c r="J44" t="n">
+        <v>13.075</v>
+      </c>
       <c r="K44" t="n">
-        <v>77.36750000000001</v>
+        <v>0.0629152869605894</v>
       </c>
       <c r="L44" t="n">
-        <v>1.79015071525649</v>
+        <v>12.55</v>
       </c>
       <c r="M44" t="n">
-        <v>13.075</v>
+        <v>0.440643468880076</v>
       </c>
       <c r="N44" t="n">
-        <v>0.0629152869605894</v>
+        <v>1.02243843544472</v>
       </c>
       <c r="O44" t="n">
-        <v>12.55</v>
+        <v>0.301409100223392</v>
       </c>
       <c r="P44" t="n">
-        <v>0.440643468880076</v>
+        <v>266.13935480484</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.02243843544472</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0.301409100223392</v>
-      </c>
-      <c r="S44" t="n">
-        <v>266.13935480484</v>
-      </c>
-      <c r="T44" t="n">
         <v>0.109011264372969</v>
       </c>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2836,31 +2189,19 @@
           <t>FAR WAA W20-01aMgmtHigh InputCvIllabo</t>
         </is>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G45" t="n">
+      <c r="D45" t="n">
         <v>0.3125</v>
       </c>
-      <c r="H45" t="n">
+      <c r="E45" t="n">
         <v>0.00853912563829967</v>
       </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
@@ -2874,9 +2215,6 @@
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr"/>
-      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2884,33 +2222,21 @@
           <t>FAR WAA W20-01aMgmtHigh InputCvIllabo</t>
         </is>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="3" t="n">
         <v>44132</v>
       </c>
       <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="n">
+        <v>1098.38662726247</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.329685606104367</v>
+      </c>
       <c r="H46" t="inlineStr"/>
-      <c r="I46" t="n">
-        <v>1098.38662726247</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0.329685606104367</v>
-      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
@@ -2922,9 +2248,6 @@
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr"/>
-      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2932,7 +2255,7 @@
           <t>FAR WAA W20-01aMgmtHigh InputCvIllabo</t>
         </is>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="3" t="n">
         <v>44161</v>
       </c>
       <c r="C47" t="inlineStr">
@@ -2940,27 +2263,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G47" t="n">
+      <c r="D47" t="n">
         <v>0.235</v>
       </c>
-      <c r="H47" t="n">
+      <c r="E47" t="n">
         <v>0.148352058743158</v>
       </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
@@ -2974,9 +2285,6 @@
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
-      <c r="W47" t="inlineStr"/>
-      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2984,7 +2292,7 @@
           <t>FAR WAA W20-01aMgmtHigh InputCvIllabo</t>
         </is>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C48" t="inlineStr">
@@ -2992,29 +2300,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="n">
+        <v>903.547095037536</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1.93039375066727</v>
+      </c>
       <c r="H48" t="inlineStr"/>
-      <c r="I48" t="n">
-        <v>903.547095037536</v>
-      </c>
-      <c r="J48" t="n">
-        <v>1.93039375066727</v>
-      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
@@ -3026,9 +2322,6 @@
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
-      <c r="W48" t="inlineStr"/>
-      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3036,7 +2329,7 @@
           <t>FAR WAA W20-01aMgmtHigh InputCvIllabo</t>
         </is>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="3" t="n">
         <v>44182</v>
       </c>
       <c r="C49" t="inlineStr">
@@ -3044,59 +2337,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+      <c r="H49" t="n">
+        <v>71.875</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.839369803284978</v>
+      </c>
+      <c r="J49" t="n">
+        <v>12.925</v>
+      </c>
       <c r="K49" t="n">
-        <v>71.875</v>
+        <v>0.08539125638299661</v>
       </c>
       <c r="L49" t="n">
-        <v>0.839369803284978</v>
+        <v>11.475</v>
       </c>
       <c r="M49" t="n">
-        <v>12.925</v>
+        <v>0.232289331079439</v>
       </c>
       <c r="N49" t="n">
-        <v>0.08539125638299661</v>
+        <v>2.04125152183631</v>
       </c>
       <c r="O49" t="n">
-        <v>11.475</v>
+        <v>0.195624377370396</v>
       </c>
       <c r="P49" t="n">
-        <v>0.232289331079439</v>
+        <v>279.121129397765</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.04125152183631</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0.195624377370396</v>
-      </c>
-      <c r="S49" t="n">
-        <v>279.121129397765</v>
-      </c>
-      <c r="T49" t="n">
         <v>0.0716523013917152</v>
       </c>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
-      <c r="W49" t="inlineStr"/>
-      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3104,31 +2382,19 @@
           <t>FAR WAA W20-01aMgmtHigh InputCvCutlass</t>
         </is>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Cutlass</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G50" t="n">
+      <c r="D50" t="n">
         <v>0.2875</v>
       </c>
-      <c r="H50" t="n">
+      <c r="E50" t="n">
         <v>0.0188745860881769</v>
       </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
@@ -3142,9 +2408,6 @@
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
-      <c r="W50" t="inlineStr"/>
-      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3152,33 +2415,21 @@
           <t>FAR WAA W20-01aMgmtHigh InputCvCutlass</t>
         </is>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="3" t="n">
         <v>44132</v>
       </c>
       <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Cutlass</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="n">
+        <v>425.550004159027</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.462205891516295</v>
+      </c>
       <c r="H51" t="inlineStr"/>
-      <c r="I51" t="n">
-        <v>425.550004159027</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0.462205891516295</v>
-      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
@@ -3190,9 +2441,6 @@
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
-      <c r="W51" t="inlineStr"/>
-      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3200,7 +2448,7 @@
           <t>FAR WAA W20-01aMgmtHigh InputCvCutlass</t>
         </is>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="3" t="n">
         <v>44161</v>
       </c>
       <c r="C52" t="inlineStr">
@@ -3208,27 +2456,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Cutlass</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G52" t="n">
+      <c r="D52" t="n">
         <v>0.1075</v>
       </c>
-      <c r="H52" t="n">
+      <c r="E52" t="n">
         <v>0.00946484724300045</v>
       </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
@@ -3242,9 +2478,6 @@
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
-      <c r="W52" t="inlineStr"/>
-      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3252,7 +2485,7 @@
           <t>FAR WAA W20-01aMgmtHigh InputCvCutlass</t>
         </is>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C53" t="inlineStr">
@@ -3260,29 +2493,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Cutlass</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="n">
+        <v>945.622872328034</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1.87380673675062</v>
+      </c>
       <c r="H53" t="inlineStr"/>
-      <c r="I53" t="n">
-        <v>945.622872328034</v>
-      </c>
-      <c r="J53" t="n">
-        <v>1.87380673675062</v>
-      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
@@ -3294,9 +2515,6 @@
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
-      <c r="W53" t="inlineStr"/>
-      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3304,7 +2522,7 @@
           <t>FAR WAA W20-01aMgmtHigh InputCvCutlass</t>
         </is>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="3" t="n">
         <v>44182</v>
       </c>
       <c r="C54" t="inlineStr">
@@ -3312,59 +2530,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Cutlass</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+      <c r="H54" t="n">
+        <v>75.53</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.814606244349585</v>
+      </c>
+      <c r="J54" t="n">
+        <v>13.05</v>
+      </c>
       <c r="K54" t="n">
-        <v>75.53</v>
+        <v>0.06454972243679009</v>
       </c>
       <c r="L54" t="n">
-        <v>0.814606244349585</v>
+        <v>11.525</v>
       </c>
       <c r="M54" t="n">
-        <v>13.05</v>
+        <v>0.349702254305955</v>
       </c>
       <c r="N54" t="n">
-        <v>0.06454972243679009</v>
+        <v>1.40233656532681</v>
       </c>
       <c r="O54" t="n">
-        <v>11.525</v>
+        <v>0.386933528431132</v>
       </c>
       <c r="P54" t="n">
-        <v>0.349702254305955</v>
+        <v>317.61510530138</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.40233656532681</v>
-      </c>
-      <c r="R54" t="n">
-        <v>0.386933528431132</v>
-      </c>
-      <c r="S54" t="n">
-        <v>317.61510530138</v>
-      </c>
-      <c r="T54" t="n">
         <v>0.0999378896477446</v>
       </c>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
-      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3372,31 +2575,19 @@
           <t>FAR WAA W20-01aMgmtHigh InputCvScepter</t>
         </is>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G55" t="n">
+      <c r="D55" t="n">
         <v>0.24</v>
       </c>
-      <c r="H55" t="n">
+      <c r="E55" t="n">
         <v>0.00707106781186548</v>
       </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
@@ -3410,9 +2601,6 @@
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
-      <c r="W55" t="inlineStr"/>
-      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3420,33 +2608,21 @@
           <t>FAR WAA W20-01aMgmtHigh InputCvScepter</t>
         </is>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="3" t="n">
         <v>44132</v>
       </c>
       <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="n">
+        <v>313.045899542233</v>
+      </c>
+      <c r="G56" t="n">
+        <v>1.05100487533618</v>
+      </c>
       <c r="H56" t="inlineStr"/>
-      <c r="I56" t="n">
-        <v>313.045899542233</v>
-      </c>
-      <c r="J56" t="n">
-        <v>1.05100487533618</v>
-      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
@@ -3458,9 +2634,6 @@
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr"/>
-      <c r="W56" t="inlineStr"/>
-      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3468,7 +2641,7 @@
           <t>FAR WAA W20-01aMgmtHigh InputCvScepter</t>
         </is>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="3" t="n">
         <v>44161</v>
       </c>
       <c r="C57" t="inlineStr">
@@ -3476,27 +2649,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G57" t="n">
+      <c r="D57" t="n">
         <v>0.0975</v>
       </c>
-      <c r="H57" t="n">
+      <c r="E57" t="n">
         <v>0.00629152869605896</v>
       </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
@@ -3510,9 +2671,6 @@
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
-      <c r="V57" t="inlineStr"/>
-      <c r="W57" t="inlineStr"/>
-      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3520,7 +2678,7 @@
           <t>FAR WAA W20-01aMgmtHigh InputCvScepter</t>
         </is>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C58" t="inlineStr">
@@ -3528,29 +2686,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="n">
+        <v>943.87705343218</v>
+      </c>
+      <c r="G58" t="n">
+        <v>1.71257050057001</v>
+      </c>
       <c r="H58" t="inlineStr"/>
-      <c r="I58" t="n">
-        <v>943.87705343218</v>
-      </c>
-      <c r="J58" t="n">
-        <v>1.71257050057001</v>
-      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
@@ -3562,9 +2708,6 @@
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
-      <c r="W58" t="inlineStr"/>
-      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3572,7 +2715,7 @@
           <t>FAR WAA W20-01aMgmtHigh InputCvScepter</t>
         </is>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="3" t="n">
         <v>44182</v>
       </c>
       <c r="C59" t="inlineStr">
@@ -3580,59 +2723,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+      <c r="H59" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.491985772152001</v>
+      </c>
+      <c r="J59" t="n">
+        <v>13</v>
+      </c>
       <c r="K59" t="n">
-        <v>78.09999999999999</v>
+        <v>0.0912870929175274</v>
       </c>
       <c r="L59" t="n">
-        <v>0.491985772152001</v>
+        <v>11.125</v>
       </c>
       <c r="M59" t="n">
-        <v>13</v>
+        <v>0.314576434802948</v>
       </c>
       <c r="N59" t="n">
-        <v>0.0912870929175274</v>
+        <v>1.48186581178704</v>
       </c>
       <c r="O59" t="n">
-        <v>11.125</v>
+        <v>0.0514665511276191</v>
       </c>
       <c r="P59" t="n">
-        <v>0.314576434802948</v>
+        <v>346.208074126572</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.48186581178704</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0.0514665511276191</v>
-      </c>
-      <c r="S59" t="n">
-        <v>346.208074126572</v>
-      </c>
-      <c r="T59" t="n">
         <v>0.15597617034688</v>
       </c>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
-      <c r="W59" t="inlineStr"/>
-      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3640,31 +2768,19 @@
           <t>FAR WAA W20-01aMgmtHigh InputCvAnapurna</t>
         </is>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G60" t="n">
+      <c r="D60" t="n">
         <v>0.3975</v>
       </c>
-      <c r="H60" t="n">
+      <c r="E60" t="n">
         <v>0.0103077640640441</v>
       </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
@@ -3678,9 +2794,6 @@
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr"/>
-      <c r="W60" t="inlineStr"/>
-      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3688,33 +2801,21 @@
           <t>FAR WAA W20-01aMgmtHigh InputCvAnapurna</t>
         </is>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="3" t="n">
         <v>44132</v>
       </c>
       <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="n">
+        <v>990.0431509286281</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.693541062374887</v>
+      </c>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="n">
-        <v>990.0431509286281</v>
-      </c>
-      <c r="J61" t="n">
-        <v>0.693541062374887</v>
-      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
@@ -3726,9 +2827,6 @@
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr"/>
-      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3736,7 +2834,7 @@
           <t>FAR WAA W20-01aMgmtHigh InputCvAnapurna</t>
         </is>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="3" t="n">
         <v>44161</v>
       </c>
       <c r="C62" t="inlineStr">
@@ -3744,27 +2842,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G62" t="n">
+      <c r="D62" t="n">
         <v>0.125</v>
       </c>
-      <c r="H62" t="n">
+      <c r="E62" t="n">
         <v>0.00288675134594813</v>
       </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
@@ -3778,9 +2864,6 @@
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr"/>
-      <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3788,7 +2871,7 @@
           <t>FAR WAA W20-01aMgmtHigh InputCvAnapurna</t>
         </is>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C63" t="inlineStr">
@@ -3796,29 +2879,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="n">
+        <v>929.69565914054</v>
+      </c>
+      <c r="G63" t="n">
+        <v>1.98405455773234</v>
+      </c>
       <c r="H63" t="inlineStr"/>
-      <c r="I63" t="n">
-        <v>929.69565914054</v>
-      </c>
-      <c r="J63" t="n">
-        <v>1.98405455773234</v>
-      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
@@ -3830,9 +2901,6 @@
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr"/>
-      <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr"/>
-      <c r="X63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3840,7 +2908,7 @@
           <t>FAR WAA W20-01aMgmtHigh InputCvAnapurna</t>
         </is>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="3" t="n">
         <v>44182</v>
       </c>
       <c r="C64" t="inlineStr">
@@ -3848,59 +2916,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+      <c r="H64" t="n">
+        <v>78.27500000000001</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1.23774324208752</v>
+      </c>
+      <c r="J64" t="n">
+        <v>13.075</v>
+      </c>
       <c r="K64" t="n">
-        <v>78.27500000000001</v>
+        <v>0.08539125638299699</v>
       </c>
       <c r="L64" t="n">
-        <v>1.23774324208752</v>
+        <v>13.275</v>
       </c>
       <c r="M64" t="n">
-        <v>13.075</v>
+        <v>0.217466472511665</v>
       </c>
       <c r="N64" t="n">
-        <v>0.08539125638299699</v>
+        <v>1.59465624505275</v>
       </c>
       <c r="O64" t="n">
-        <v>13.275</v>
+        <v>0.0644660204324228</v>
       </c>
       <c r="P64" t="n">
-        <v>0.217466472511665</v>
+        <v>282.619200111995</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.59465624505275</v>
-      </c>
-      <c r="R64" t="n">
-        <v>0.0644660204324228</v>
-      </c>
-      <c r="S64" t="n">
-        <v>282.619200111995</v>
-      </c>
-      <c r="T64" t="n">
         <v>0.11662600581546</v>
       </c>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr"/>
-      <c r="V64" t="inlineStr"/>
-      <c r="W64" t="inlineStr"/>
-      <c r="X64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3908,31 +2961,19 @@
           <t>FAR WAA W20-01aMgmtHigh InputCvPascal</t>
         </is>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Pascal</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G65" t="n">
+      <c r="D65" t="n">
         <v>0.2425</v>
       </c>
-      <c r="H65" t="n">
+      <c r="E65" t="n">
         <v>0.0125</v>
       </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
@@ -3946,9 +2987,6 @@
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr"/>
-      <c r="V65" t="inlineStr"/>
-      <c r="W65" t="inlineStr"/>
-      <c r="X65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3956,33 +2994,21 @@
           <t>FAR WAA W20-01aMgmtHigh InputCvPascal</t>
         </is>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="3" t="n">
         <v>44132</v>
       </c>
       <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Pascal</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="n">
+        <v>424.483784947211</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.295621784059126</v>
+      </c>
       <c r="H66" t="inlineStr"/>
-      <c r="I66" t="n">
-        <v>424.483784947211</v>
-      </c>
-      <c r="J66" t="n">
-        <v>0.295621784059126</v>
-      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
@@ -3994,9 +3020,6 @@
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
       <c r="U66" t="inlineStr"/>
-      <c r="V66" t="inlineStr"/>
-      <c r="W66" t="inlineStr"/>
-      <c r="X66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4004,7 +3027,7 @@
           <t>FAR WAA W20-01aMgmtHigh InputCvPascal</t>
         </is>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="3" t="n">
         <v>44161</v>
       </c>
       <c r="C67" t="inlineStr">
@@ -4012,27 +3035,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Pascal</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G67" t="n">
+      <c r="D67" t="n">
         <v>0.1025</v>
       </c>
-      <c r="H67" t="n">
+      <c r="E67" t="n">
         <v>0.0025</v>
       </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
@@ -4046,9 +3057,6 @@
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
-      <c r="V67" t="inlineStr"/>
-      <c r="W67" t="inlineStr"/>
-      <c r="X67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4056,7 +3064,7 @@
           <t>FAR WAA W20-01aMgmtHigh InputCvPascal</t>
         </is>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C68" t="inlineStr">
@@ -4064,29 +3072,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Pascal</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="n">
+        <v>726.155496762544</v>
+      </c>
+      <c r="G68" t="n">
+        <v>1.89668127649037</v>
+      </c>
       <c r="H68" t="inlineStr"/>
-      <c r="I68" t="n">
-        <v>726.155496762544</v>
-      </c>
-      <c r="J68" t="n">
-        <v>1.89668127649037</v>
-      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
@@ -4098,9 +3094,6 @@
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
-      <c r="V68" t="inlineStr"/>
-      <c r="W68" t="inlineStr"/>
-      <c r="X68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4108,7 +3101,7 @@
           <t>FAR WAA W20-01aMgmtHigh InputCvPascal</t>
         </is>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="3" t="n">
         <v>44182</v>
       </c>
       <c r="C69" t="inlineStr">
@@ -4116,59 +3109,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Pascal</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+      <c r="H69" t="n">
+        <v>73.75749999999999</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.742701992726558</v>
+      </c>
+      <c r="J69" t="n">
+        <v>12.75</v>
+      </c>
       <c r="K69" t="n">
-        <v>73.75749999999999</v>
+        <v>0.08660254037844391</v>
       </c>
       <c r="L69" t="n">
-        <v>0.742701992726558</v>
+        <v>11.925</v>
       </c>
       <c r="M69" t="n">
-        <v>12.75</v>
+        <v>0.193110503770941</v>
       </c>
       <c r="N69" t="n">
-        <v>0.08660254037844391</v>
+        <v>1.53888252238687</v>
       </c>
       <c r="O69" t="n">
-        <v>11.925</v>
+        <v>0.168104279241192</v>
       </c>
       <c r="P69" t="n">
-        <v>0.193110503770941</v>
+        <v>250.516313620495</v>
       </c>
       <c r="Q69" t="n">
-        <v>1.53888252238687</v>
-      </c>
-      <c r="R69" t="n">
-        <v>0.168104279241192</v>
-      </c>
-      <c r="S69" t="n">
-        <v>250.516313620495</v>
-      </c>
-      <c r="T69" t="n">
         <v>0.0919111003665263</v>
       </c>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr"/>
-      <c r="V69" t="inlineStr"/>
-      <c r="W69" t="inlineStr"/>
-      <c r="X69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4176,31 +3154,19 @@
           <t>FAR WAA W20-01aMgmtHigh InputCvMowhawk</t>
         </is>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Mowhawk</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G70" t="n">
+      <c r="D70" t="n">
         <v>0.26</v>
       </c>
-      <c r="H70" t="n">
+      <c r="E70" t="n">
         <v>0.00912870929175278</v>
       </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
@@ -4214,9 +3180,6 @@
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr"/>
-      <c r="V70" t="inlineStr"/>
-      <c r="W70" t="inlineStr"/>
-      <c r="X70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4224,33 +3187,21 @@
           <t>FAR WAA W20-01aMgmtHigh InputCvMowhawk</t>
         </is>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="3" t="n">
         <v>44132</v>
       </c>
       <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Mowhawk</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="n">
+        <v>1208.84446974861</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.270590570601867</v>
+      </c>
       <c r="H71" t="inlineStr"/>
-      <c r="I71" t="n">
-        <v>1208.84446974861</v>
-      </c>
-      <c r="J71" t="n">
-        <v>0.270590570601867</v>
-      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
@@ -4262,9 +3213,6 @@
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr"/>
-      <c r="V71" t="inlineStr"/>
-      <c r="W71" t="inlineStr"/>
-      <c r="X71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4272,7 +3220,7 @@
           <t>FAR WAA W20-01aMgmtHigh InputCvMowhawk</t>
         </is>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="3" t="n">
         <v>44161</v>
       </c>
       <c r="C72" t="inlineStr">
@@ -4280,27 +3228,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Mowhawk</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G72" t="n">
+      <c r="D72" t="n">
         <v>0.115</v>
       </c>
-      <c r="H72" t="n">
+      <c r="E72" t="n">
         <v>0.005</v>
       </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
@@ -4314,9 +3250,6 @@
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr"/>
-      <c r="V72" t="inlineStr"/>
-      <c r="W72" t="inlineStr"/>
-      <c r="X72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4324,7 +3257,7 @@
           <t>FAR WAA W20-01aMgmtHigh InputCvMowhawk</t>
         </is>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C73" t="inlineStr">
@@ -4332,29 +3265,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Mowhawk</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="n">
+        <v>950.742200533867</v>
+      </c>
+      <c r="G73" t="n">
+        <v>1.79220873104067</v>
+      </c>
       <c r="H73" t="inlineStr"/>
-      <c r="I73" t="n">
-        <v>950.742200533867</v>
-      </c>
-      <c r="J73" t="n">
-        <v>1.79220873104067</v>
-      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
@@ -4366,9 +3287,6 @@
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr"/>
-      <c r="V73" t="inlineStr"/>
-      <c r="W73" t="inlineStr"/>
-      <c r="X73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4376,7 +3294,7 @@
           <t>FAR WAA W20-01aMgmtHigh InputCvMowhawk</t>
         </is>
       </c>
-      <c r="B74" s="1" t="n">
+      <c r="B74" s="3" t="n">
         <v>44182</v>
       </c>
       <c r="C74" t="inlineStr">
@@ -4384,59 +3302,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Mowhawk</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
+      <c r="H74" t="n">
+        <v>75.2975</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.843004300107656</v>
+      </c>
+      <c r="J74" t="n">
+        <v>12.875</v>
+      </c>
       <c r="K74" t="n">
-        <v>75.2975</v>
+        <v>0.0478713553878168</v>
       </c>
       <c r="L74" t="n">
-        <v>0.843004300107656</v>
+        <v>11.8</v>
       </c>
       <c r="M74" t="n">
-        <v>12.875</v>
+        <v>0.0408248290463865</v>
       </c>
       <c r="N74" t="n">
-        <v>0.0478713553878168</v>
+        <v>2.07446573549174</v>
       </c>
       <c r="O74" t="n">
-        <v>11.8</v>
+        <v>0.338728539445291</v>
       </c>
       <c r="P74" t="n">
-        <v>0.0408248290463865</v>
+        <v>326.193258009492</v>
       </c>
       <c r="Q74" t="n">
-        <v>2.07446573549174</v>
-      </c>
-      <c r="R74" t="n">
-        <v>0.338728539445291</v>
-      </c>
-      <c r="S74" t="n">
-        <v>326.193258009492</v>
-      </c>
-      <c r="T74" t="n">
         <v>0.191174394810386</v>
       </c>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr"/>
-      <c r="V74" t="inlineStr"/>
-      <c r="W74" t="inlineStr"/>
-      <c r="X74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4444,25 +3347,13 @@
           <t>FAR WAA W20-01aMgmtStandardCvScepter</t>
         </is>
       </c>
-      <c r="B75" s="1" t="n">
+      <c r="B75" s="3" t="n">
         <v>43997</v>
       </c>
       <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
@@ -4474,17 +3365,14 @@
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr"/>
-      <c r="S75" t="inlineStr"/>
+      <c r="R75" t="n">
+        <v>123.888888888889</v>
+      </c>
+      <c r="S75" t="n">
+        <v>7.44665528254941</v>
+      </c>
       <c r="T75" t="inlineStr"/>
-      <c r="U75" t="n">
-        <v>123.888888888889</v>
-      </c>
-      <c r="V75" t="n">
-        <v>7.44665528254941</v>
-      </c>
-      <c r="W75" t="inlineStr"/>
-      <c r="X75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4492,25 +3380,13 @@
           <t>FAR WAA W20-01aMgmtStandardCvScepter</t>
         </is>
       </c>
-      <c r="B76" s="1" t="n">
+      <c r="B76" s="3" t="n">
         <v>44105</v>
       </c>
       <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
@@ -4524,13 +3400,10 @@
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr"/>
-      <c r="T76" t="inlineStr"/>
-      <c r="U76" t="inlineStr"/>
-      <c r="V76" t="inlineStr"/>
-      <c r="W76" t="n">
+      <c r="T76" t="n">
         <v>233.888888888889</v>
       </c>
-      <c r="X76" t="n">
+      <c r="U76" t="n">
         <v>23.5942205380545</v>
       </c>
     </row>
@@ -4540,31 +3413,19 @@
           <t>FAR WAA W20-01aMgmtStandardCvScepter</t>
         </is>
       </c>
-      <c r="B77" s="1" t="n">
+      <c r="B77" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="C77" t="inlineStr"/>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G77" t="n">
+      <c r="D77" t="n">
         <v>0.2375</v>
       </c>
-      <c r="H77" t="n">
+      <c r="E77" t="n">
         <v>0.0075</v>
       </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
@@ -4578,9 +3439,6 @@
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
       <c r="U77" t="inlineStr"/>
-      <c r="V77" t="inlineStr"/>
-      <c r="W77" t="inlineStr"/>
-      <c r="X77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4588,33 +3446,21 @@
           <t>FAR WAA W20-01aMgmtStandardCvScepter</t>
         </is>
       </c>
-      <c r="B78" s="1" t="n">
+      <c r="B78" s="3" t="n">
         <v>44132</v>
       </c>
       <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="n">
+        <v>396.619811242635</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.234011127144344</v>
+      </c>
       <c r="H78" t="inlineStr"/>
-      <c r="I78" t="n">
-        <v>396.619811242635</v>
-      </c>
-      <c r="J78" t="n">
-        <v>0.234011127144344</v>
-      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
@@ -4626,9 +3472,6 @@
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
       <c r="U78" t="inlineStr"/>
-      <c r="V78" t="inlineStr"/>
-      <c r="W78" t="inlineStr"/>
-      <c r="X78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4636,7 +3479,7 @@
           <t>FAR WAA W20-01aMgmtStandardCvScepter</t>
         </is>
       </c>
-      <c r="B79" s="1" t="n">
+      <c r="B79" s="3" t="n">
         <v>44161</v>
       </c>
       <c r="C79" t="inlineStr">
@@ -4644,27 +3487,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G79" t="n">
+      <c r="D79" t="n">
         <v>0.11</v>
       </c>
-      <c r="H79" t="n">
+      <c r="E79" t="n">
         <v>0.00408248290463863</v>
       </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
@@ -4678,9 +3509,6 @@
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="inlineStr"/>
       <c r="U79" t="inlineStr"/>
-      <c r="V79" t="inlineStr"/>
-      <c r="W79" t="inlineStr"/>
-      <c r="X79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4688,7 +3516,7 @@
           <t>FAR WAA W20-01aMgmtStandardCvScepter</t>
         </is>
       </c>
-      <c r="B80" s="1" t="n">
+      <c r="B80" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C80" t="inlineStr">
@@ -4696,29 +3524,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="n">
+        <v>853.015956962219</v>
+      </c>
+      <c r="G80" t="n">
+        <v>1.53571298604228</v>
+      </c>
       <c r="H80" t="inlineStr"/>
-      <c r="I80" t="n">
-        <v>853.015956962219</v>
-      </c>
-      <c r="J80" t="n">
-        <v>1.53571298604228</v>
-      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
@@ -4730,9 +3546,6 @@
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="inlineStr"/>
       <c r="U80" t="inlineStr"/>
-      <c r="V80" t="inlineStr"/>
-      <c r="W80" t="inlineStr"/>
-      <c r="X80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4740,7 +3553,7 @@
           <t>FAR WAA W20-01aMgmtStandardCvScepter</t>
         </is>
       </c>
-      <c r="B81" s="1" t="n">
+      <c r="B81" s="3" t="n">
         <v>44182</v>
       </c>
       <c r="C81" t="inlineStr">
@@ -4748,59 +3561,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
+      <c r="H81" t="n">
+        <v>79.28749999999999</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.430762405509112</v>
+      </c>
+      <c r="J81" t="n">
+        <v>13.025</v>
+      </c>
       <c r="K81" t="n">
-        <v>79.28749999999999</v>
+        <v>0.09464847243000481</v>
       </c>
       <c r="L81" t="n">
-        <v>0.430762405509112</v>
+        <v>10.7</v>
       </c>
       <c r="M81" t="n">
-        <v>13.025</v>
+        <v>0.234520787991172</v>
       </c>
       <c r="N81" t="n">
-        <v>0.09464847243000481</v>
+        <v>1.14607568185815</v>
       </c>
       <c r="O81" t="n">
-        <v>10.7</v>
+        <v>0.233474186456422</v>
       </c>
       <c r="P81" t="n">
-        <v>0.234520787991172</v>
+        <v>340.45626657209</v>
       </c>
       <c r="Q81" t="n">
-        <v>1.14607568185815</v>
-      </c>
-      <c r="R81" t="n">
-        <v>0.233474186456422</v>
-      </c>
-      <c r="S81" t="n">
-        <v>340.45626657209</v>
-      </c>
-      <c r="T81" t="n">
         <v>0.217476517238371</v>
       </c>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
       <c r="U81" t="inlineStr"/>
-      <c r="V81" t="inlineStr"/>
-      <c r="W81" t="inlineStr"/>
-      <c r="X81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4808,25 +3606,13 @@
           <t>FAR WAA W20-01aMgmtStandardCvCutlass</t>
         </is>
       </c>
-      <c r="B82" s="1" t="n">
+      <c r="B82" s="3" t="n">
         <v>43997</v>
       </c>
       <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Cutlass</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
@@ -4838,17 +3624,14 @@
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr"/>
-      <c r="S82" t="inlineStr"/>
+      <c r="R82" t="n">
+        <v>168.333333333333</v>
+      </c>
+      <c r="S82" t="n">
+        <v>14.3551370194693</v>
+      </c>
       <c r="T82" t="inlineStr"/>
-      <c r="U82" t="n">
-        <v>168.333333333333</v>
-      </c>
-      <c r="V82" t="n">
-        <v>14.3551370194693</v>
-      </c>
-      <c r="W82" t="inlineStr"/>
-      <c r="X82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4856,25 +3639,13 @@
           <t>FAR WAA W20-01aMgmtStandardCvCutlass</t>
         </is>
       </c>
-      <c r="B83" s="1" t="n">
+      <c r="B83" s="3" t="n">
         <v>44105</v>
       </c>
       <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Cutlass</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
@@ -4888,13 +3659,10 @@
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr"/>
-      <c r="T83" t="inlineStr"/>
-      <c r="U83" t="inlineStr"/>
-      <c r="V83" t="inlineStr"/>
-      <c r="W83" t="n">
+      <c r="T83" t="n">
         <v>262.222222222222</v>
       </c>
-      <c r="X83" t="n">
+      <c r="U83" t="n">
         <v>23.5876790045788</v>
       </c>
     </row>
@@ -4904,31 +3672,19 @@
           <t>FAR WAA W20-01aMgmtStandardCvCutlass</t>
         </is>
       </c>
-      <c r="B84" s="1" t="n">
+      <c r="B84" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Cutlass</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G84" t="n">
+      <c r="D84" t="n">
         <v>0.27</v>
       </c>
-      <c r="H84" t="n">
+      <c r="E84" t="n">
         <v>0.0115470053837925</v>
       </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
@@ -4942,9 +3698,6 @@
       <c r="S84" t="inlineStr"/>
       <c r="T84" t="inlineStr"/>
       <c r="U84" t="inlineStr"/>
-      <c r="V84" t="inlineStr"/>
-      <c r="W84" t="inlineStr"/>
-      <c r="X84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4952,33 +3705,21 @@
           <t>FAR WAA W20-01aMgmtStandardCvCutlass</t>
         </is>
       </c>
-      <c r="B85" s="1" t="n">
+      <c r="B85" s="3" t="n">
         <v>44132</v>
       </c>
       <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Cutlass</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr"/>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="n">
+        <v>443.605965245778</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.292051074375893</v>
+      </c>
       <c r="H85" t="inlineStr"/>
-      <c r="I85" t="n">
-        <v>443.605965245778</v>
-      </c>
-      <c r="J85" t="n">
-        <v>0.292051074375893</v>
-      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr"/>
@@ -4990,9 +3731,6 @@
       <c r="S85" t="inlineStr"/>
       <c r="T85" t="inlineStr"/>
       <c r="U85" t="inlineStr"/>
-      <c r="V85" t="inlineStr"/>
-      <c r="W85" t="inlineStr"/>
-      <c r="X85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5000,7 +3738,7 @@
           <t>FAR WAA W20-01aMgmtStandardCvCutlass</t>
         </is>
       </c>
-      <c r="B86" s="1" t="n">
+      <c r="B86" s="3" t="n">
         <v>44161</v>
       </c>
       <c r="C86" t="inlineStr">
@@ -5008,27 +3746,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Cutlass</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G86" t="n">
+      <c r="D86" t="n">
         <v>0.105</v>
       </c>
-      <c r="H86" t="n">
+      <c r="E86" t="n">
         <v>0.005</v>
       </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
@@ -5042,9 +3768,6 @@
       <c r="S86" t="inlineStr"/>
       <c r="T86" t="inlineStr"/>
       <c r="U86" t="inlineStr"/>
-      <c r="V86" t="inlineStr"/>
-      <c r="W86" t="inlineStr"/>
-      <c r="X86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5052,7 +3775,7 @@
           <t>FAR WAA W20-01aMgmtStandardCvCutlass</t>
         </is>
       </c>
-      <c r="B87" s="1" t="n">
+      <c r="B87" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C87" t="inlineStr">
@@ -5060,29 +3783,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Cutlass</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="n">
+        <v>785.245633290654</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1.60136216765456</v>
+      </c>
       <c r="H87" t="inlineStr"/>
-      <c r="I87" t="n">
-        <v>785.245633290654</v>
-      </c>
-      <c r="J87" t="n">
-        <v>1.60136216765456</v>
-      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr"/>
@@ -5094,9 +3805,6 @@
       <c r="S87" t="inlineStr"/>
       <c r="T87" t="inlineStr"/>
       <c r="U87" t="inlineStr"/>
-      <c r="V87" t="inlineStr"/>
-      <c r="W87" t="inlineStr"/>
-      <c r="X87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5104,7 +3812,7 @@
           <t>FAR WAA W20-01aMgmtStandardCvCutlass</t>
         </is>
       </c>
-      <c r="B88" s="1" t="n">
+      <c r="B88" s="3" t="n">
         <v>44182</v>
       </c>
       <c r="C88" t="inlineStr">
@@ -5112,59 +3820,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Cutlass</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
+      <c r="H88" t="n">
+        <v>76.1525</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0.166602070815462</v>
+      </c>
+      <c r="J88" t="n">
+        <v>12.975</v>
+      </c>
       <c r="K88" t="n">
-        <v>76.1525</v>
+        <v>0.149303940559741</v>
       </c>
       <c r="L88" t="n">
-        <v>0.166602070815462</v>
+        <v>10.675</v>
       </c>
       <c r="M88" t="n">
-        <v>12.975</v>
+        <v>0.363719214046586</v>
       </c>
       <c r="N88" t="n">
-        <v>0.149303940559741</v>
+        <v>1.15956159809875</v>
       </c>
       <c r="O88" t="n">
-        <v>10.675</v>
+        <v>0.106599371051726</v>
       </c>
       <c r="P88" t="n">
-        <v>0.363719214046586</v>
+        <v>283.670533185999</v>
       </c>
       <c r="Q88" t="n">
-        <v>1.15956159809875</v>
-      </c>
-      <c r="R88" t="n">
-        <v>0.106599371051726</v>
-      </c>
-      <c r="S88" t="n">
-        <v>283.670533185999</v>
-      </c>
-      <c r="T88" t="n">
         <v>0.149873841403698</v>
       </c>
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="inlineStr"/>
+      <c r="T88" t="inlineStr"/>
       <c r="U88" t="inlineStr"/>
-      <c r="V88" t="inlineStr"/>
-      <c r="W88" t="inlineStr"/>
-      <c r="X88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5172,25 +3865,13 @@
           <t>FAR WAA W20-01aMgmtStandardCvPascal</t>
         </is>
       </c>
-      <c r="B89" s="1" t="n">
+      <c r="B89" s="3" t="n">
         <v>43997</v>
       </c>
       <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Pascal</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
@@ -5202,17 +3883,14 @@
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr"/>
       <c r="Q89" t="inlineStr"/>
-      <c r="R89" t="inlineStr"/>
-      <c r="S89" t="inlineStr"/>
+      <c r="R89" t="n">
+        <v>147.222222222222</v>
+      </c>
+      <c r="S89" t="n">
+        <v>26.3776779304796</v>
+      </c>
       <c r="T89" t="inlineStr"/>
-      <c r="U89" t="n">
-        <v>147.222222222222</v>
-      </c>
-      <c r="V89" t="n">
-        <v>26.3776779304796</v>
-      </c>
-      <c r="W89" t="inlineStr"/>
-      <c r="X89" t="inlineStr"/>
+      <c r="U89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5220,25 +3898,13 @@
           <t>FAR WAA W20-01aMgmtStandardCvPascal</t>
         </is>
       </c>
-      <c r="B90" s="1" t="n">
+      <c r="B90" s="3" t="n">
         <v>44105</v>
       </c>
       <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Pascal</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
@@ -5252,13 +3918,10 @@
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr"/>
       <c r="S90" t="inlineStr"/>
-      <c r="T90" t="inlineStr"/>
-      <c r="U90" t="inlineStr"/>
-      <c r="V90" t="inlineStr"/>
-      <c r="W90" t="n">
+      <c r="T90" t="n">
         <v>269.444444444445</v>
       </c>
-      <c r="X90" t="n">
+      <c r="U90" t="n">
         <v>16.2636457425603</v>
       </c>
     </row>
@@ -5268,31 +3931,19 @@
           <t>FAR WAA W20-01aMgmtStandardCvPascal</t>
         </is>
       </c>
-      <c r="B91" s="1" t="n">
+      <c r="B91" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Pascal</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G91" t="n">
+      <c r="D91" t="n">
         <v>0.235</v>
       </c>
-      <c r="H91" t="n">
+      <c r="E91" t="n">
         <v>0.00957427107756339</v>
       </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
@@ -5306,9 +3957,6 @@
       <c r="S91" t="inlineStr"/>
       <c r="T91" t="inlineStr"/>
       <c r="U91" t="inlineStr"/>
-      <c r="V91" t="inlineStr"/>
-      <c r="W91" t="inlineStr"/>
-      <c r="X91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5316,33 +3964,21 @@
           <t>FAR WAA W20-01aMgmtStandardCvPascal</t>
         </is>
       </c>
-      <c r="B92" s="1" t="n">
+      <c r="B92" s="3" t="n">
         <v>44132</v>
       </c>
       <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Pascal</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr"/>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="n">
+        <v>366.234449728734</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0.349992906157195</v>
+      </c>
       <c r="H92" t="inlineStr"/>
-      <c r="I92" t="n">
-        <v>366.234449728734</v>
-      </c>
-      <c r="J92" t="n">
-        <v>0.349992906157195</v>
-      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
@@ -5354,9 +3990,6 @@
       <c r="S92" t="inlineStr"/>
       <c r="T92" t="inlineStr"/>
       <c r="U92" t="inlineStr"/>
-      <c r="V92" t="inlineStr"/>
-      <c r="W92" t="inlineStr"/>
-      <c r="X92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5364,7 +3997,7 @@
           <t>FAR WAA W20-01aMgmtStandardCvPascal</t>
         </is>
       </c>
-      <c r="B93" s="1" t="n">
+      <c r="B93" s="3" t="n">
         <v>44161</v>
       </c>
       <c r="C93" t="inlineStr">
@@ -5372,27 +4005,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Pascal</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G93" t="n">
+      <c r="D93" t="n">
         <v>0.1075</v>
       </c>
-      <c r="H93" t="n">
+      <c r="E93" t="n">
         <v>0.00478713553878169</v>
       </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
@@ -5406,9 +4027,6 @@
       <c r="S93" t="inlineStr"/>
       <c r="T93" t="inlineStr"/>
       <c r="U93" t="inlineStr"/>
-      <c r="V93" t="inlineStr"/>
-      <c r="W93" t="inlineStr"/>
-      <c r="X93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5416,7 +4034,7 @@
           <t>FAR WAA W20-01aMgmtStandardCvPascal</t>
         </is>
       </c>
-      <c r="B94" s="1" t="n">
+      <c r="B94" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C94" t="inlineStr">
@@ -5424,29 +4042,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Pascal</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr"/>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="n">
+        <v>809.5275286742771</v>
+      </c>
+      <c r="G94" t="n">
+        <v>1.0475592837575</v>
+      </c>
       <c r="H94" t="inlineStr"/>
-      <c r="I94" t="n">
-        <v>809.5275286742771</v>
-      </c>
-      <c r="J94" t="n">
-        <v>1.0475592837575</v>
-      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
@@ -5458,9 +4064,6 @@
       <c r="S94" t="inlineStr"/>
       <c r="T94" t="inlineStr"/>
       <c r="U94" t="inlineStr"/>
-      <c r="V94" t="inlineStr"/>
-      <c r="W94" t="inlineStr"/>
-      <c r="X94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5468,7 +4071,7 @@
           <t>FAR WAA W20-01aMgmtStandardCvPascal</t>
         </is>
       </c>
-      <c r="B95" s="1" t="n">
+      <c r="B95" s="3" t="n">
         <v>44182</v>
       </c>
       <c r="C95" t="inlineStr">
@@ -5476,59 +4079,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Pascal</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
+      <c r="H95" t="n">
+        <v>74.875</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0.924278998282807</v>
+      </c>
+      <c r="J95" t="n">
+        <v>12.775</v>
+      </c>
       <c r="K95" t="n">
-        <v>74.875</v>
+        <v>0.0853912563829969</v>
       </c>
       <c r="L95" t="n">
-        <v>0.924278998282807</v>
+        <v>11.525</v>
       </c>
       <c r="M95" t="n">
-        <v>12.775</v>
+        <v>0.149303940559741</v>
       </c>
       <c r="N95" t="n">
-        <v>0.0853912563829969</v>
+        <v>1.4468055162967</v>
       </c>
       <c r="O95" t="n">
-        <v>11.525</v>
+        <v>0.162589577656568</v>
       </c>
       <c r="P95" t="n">
-        <v>0.149303940559741</v>
+        <v>252.154160544493</v>
       </c>
       <c r="Q95" t="n">
-        <v>1.4468055162967</v>
-      </c>
-      <c r="R95" t="n">
-        <v>0.162589577656568</v>
-      </c>
-      <c r="S95" t="n">
-        <v>252.154160544493</v>
-      </c>
-      <c r="T95" t="n">
         <v>0.128461776965779</v>
       </c>
+      <c r="R95" t="inlineStr"/>
+      <c r="S95" t="inlineStr"/>
+      <c r="T95" t="inlineStr"/>
       <c r="U95" t="inlineStr"/>
-      <c r="V95" t="inlineStr"/>
-      <c r="W95" t="inlineStr"/>
-      <c r="X95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5536,25 +4124,13 @@
           <t>FAR WAA W20-01aMgmtStandardCvMowhawk</t>
         </is>
       </c>
-      <c r="B96" s="1" t="n">
+      <c r="B96" s="3" t="n">
         <v>43997</v>
       </c>
       <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Mowhawk</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
@@ -5566,17 +4142,14 @@
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr"/>
       <c r="Q96" t="inlineStr"/>
-      <c r="R96" t="inlineStr"/>
-      <c r="S96" t="inlineStr"/>
+      <c r="R96" t="n">
+        <v>136.666666666667</v>
+      </c>
+      <c r="S96" t="n">
+        <v>8.43761907399583</v>
+      </c>
       <c r="T96" t="inlineStr"/>
-      <c r="U96" t="n">
-        <v>136.666666666667</v>
-      </c>
-      <c r="V96" t="n">
-        <v>8.43761907399583</v>
-      </c>
-      <c r="W96" t="inlineStr"/>
-      <c r="X96" t="inlineStr"/>
+      <c r="U96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5584,25 +4157,13 @@
           <t>FAR WAA W20-01aMgmtStandardCvMowhawk</t>
         </is>
       </c>
-      <c r="B97" s="1" t="n">
+      <c r="B97" s="3" t="n">
         <v>44105</v>
       </c>
       <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Mowhawk</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
@@ -5616,13 +4177,10 @@
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr"/>
       <c r="S97" t="inlineStr"/>
-      <c r="T97" t="inlineStr"/>
-      <c r="U97" t="inlineStr"/>
-      <c r="V97" t="inlineStr"/>
-      <c r="W97" t="n">
+      <c r="T97" t="n">
         <v>399.444444444445</v>
       </c>
-      <c r="X97" t="n">
+      <c r="U97" t="n">
         <v>37.2553749539978</v>
       </c>
     </row>
@@ -5632,31 +4190,19 @@
           <t>FAR WAA W20-01aMgmtStandardCvMowhawk</t>
         </is>
       </c>
-      <c r="B98" s="1" t="n">
+      <c r="B98" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Mowhawk</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G98" t="n">
+      <c r="D98" t="n">
         <v>0.25</v>
       </c>
-      <c r="H98" t="n">
+      <c r="E98" t="n">
         <v>0.00707106781186548</v>
       </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
@@ -5670,9 +4216,6 @@
       <c r="S98" t="inlineStr"/>
       <c r="T98" t="inlineStr"/>
       <c r="U98" t="inlineStr"/>
-      <c r="V98" t="inlineStr"/>
-      <c r="W98" t="inlineStr"/>
-      <c r="X98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5680,33 +4223,21 @@
           <t>FAR WAA W20-01aMgmtStandardCvMowhawk</t>
         </is>
       </c>
-      <c r="B99" s="1" t="n">
+      <c r="B99" s="3" t="n">
         <v>44132</v>
       </c>
       <c r="C99" t="inlineStr"/>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Mowhawk</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr"/>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="n">
+        <v>1036.03582395519</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0.764411104952986</v>
+      </c>
       <c r="H99" t="inlineStr"/>
-      <c r="I99" t="n">
-        <v>1036.03582395519</v>
-      </c>
-      <c r="J99" t="n">
-        <v>0.764411104952986</v>
-      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr"/>
@@ -5718,9 +4249,6 @@
       <c r="S99" t="inlineStr"/>
       <c r="T99" t="inlineStr"/>
       <c r="U99" t="inlineStr"/>
-      <c r="V99" t="inlineStr"/>
-      <c r="W99" t="inlineStr"/>
-      <c r="X99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5728,7 +4256,7 @@
           <t>FAR WAA W20-01aMgmtStandardCvMowhawk</t>
         </is>
       </c>
-      <c r="B100" s="1" t="n">
+      <c r="B100" s="3" t="n">
         <v>44161</v>
       </c>
       <c r="C100" t="inlineStr">
@@ -5736,27 +4264,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Mowhawk</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G100" t="n">
+      <c r="D100" t="n">
         <v>0.1125</v>
       </c>
-      <c r="H100" t="n">
+      <c r="E100" t="n">
         <v>0.00629152869605896</v>
       </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
@@ -5770,9 +4286,6 @@
       <c r="S100" t="inlineStr"/>
       <c r="T100" t="inlineStr"/>
       <c r="U100" t="inlineStr"/>
-      <c r="V100" t="inlineStr"/>
-      <c r="W100" t="inlineStr"/>
-      <c r="X100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5780,7 +4293,7 @@
           <t>FAR WAA W20-01aMgmtStandardCvMowhawk</t>
         </is>
       </c>
-      <c r="B101" s="1" t="n">
+      <c r="B101" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C101" t="inlineStr">
@@ -5788,29 +4301,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Mowhawk</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr"/>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="n">
+        <v>1115.35292749579</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0.342269393269813</v>
+      </c>
       <c r="H101" t="inlineStr"/>
-      <c r="I101" t="n">
-        <v>1115.35292749579</v>
-      </c>
-      <c r="J101" t="n">
-        <v>0.342269393269813</v>
-      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr"/>
@@ -5822,9 +4323,6 @@
       <c r="S101" t="inlineStr"/>
       <c r="T101" t="inlineStr"/>
       <c r="U101" t="inlineStr"/>
-      <c r="V101" t="inlineStr"/>
-      <c r="W101" t="inlineStr"/>
-      <c r="X101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5832,7 +4330,7 @@
           <t>FAR WAA W20-01aMgmtStandardCvMowhawk</t>
         </is>
       </c>
-      <c r="B102" s="1" t="n">
+      <c r="B102" s="3" t="n">
         <v>44182</v>
       </c>
       <c r="C102" t="inlineStr">
@@ -5840,59 +4338,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Mowhawk</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
+      <c r="H102" t="n">
+        <v>77.6225</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0.07004462863060799</v>
+      </c>
+      <c r="J102" t="n">
+        <v>12.825</v>
+      </c>
       <c r="K102" t="n">
-        <v>77.6225</v>
+        <v>0.08539125638299699</v>
       </c>
       <c r="L102" t="n">
-        <v>0.07004462863060799</v>
+        <v>10.15</v>
       </c>
       <c r="M102" t="n">
-        <v>12.825</v>
+        <v>0.232737334062816</v>
       </c>
       <c r="N102" t="n">
-        <v>0.08539125638299699</v>
+        <v>1.57508693591158</v>
       </c>
       <c r="O102" t="n">
-        <v>10.15</v>
+        <v>0.174261639305348</v>
       </c>
       <c r="P102" t="n">
-        <v>0.232737334062816</v>
+        <v>331.329137816086</v>
       </c>
       <c r="Q102" t="n">
-        <v>1.57508693591158</v>
-      </c>
-      <c r="R102" t="n">
-        <v>0.174261639305348</v>
-      </c>
-      <c r="S102" t="n">
-        <v>331.329137816086</v>
-      </c>
-      <c r="T102" t="n">
         <v>0.140054047098682</v>
       </c>
+      <c r="R102" t="inlineStr"/>
+      <c r="S102" t="inlineStr"/>
+      <c r="T102" t="inlineStr"/>
       <c r="U102" t="inlineStr"/>
-      <c r="V102" t="inlineStr"/>
-      <c r="W102" t="inlineStr"/>
-      <c r="X102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5900,25 +4383,13 @@
           <t>FAR WAA W20-01aMgmtStandardCvAccroc</t>
         </is>
       </c>
-      <c r="B103" s="1" t="n">
+      <c r="B103" s="3" t="n">
         <v>43997</v>
       </c>
       <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
@@ -5930,17 +4401,14 @@
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr"/>
       <c r="Q103" t="inlineStr"/>
-      <c r="R103" t="inlineStr"/>
-      <c r="S103" t="inlineStr"/>
+      <c r="R103" t="n">
+        <v>142.222222222222</v>
+      </c>
+      <c r="S103" t="n">
+        <v>16.8263950986674</v>
+      </c>
       <c r="T103" t="inlineStr"/>
-      <c r="U103" t="n">
-        <v>142.222222222222</v>
-      </c>
-      <c r="V103" t="n">
-        <v>16.8263950986674</v>
-      </c>
-      <c r="W103" t="inlineStr"/>
-      <c r="X103" t="inlineStr"/>
+      <c r="U103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5948,25 +4416,13 @@
           <t>FAR WAA W20-01aMgmtStandardCvAccroc</t>
         </is>
       </c>
-      <c r="B104" s="1" t="n">
+      <c r="B104" s="3" t="n">
         <v>44105</v>
       </c>
       <c r="C104" t="inlineStr"/>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
@@ -5980,13 +4436,10 @@
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr"/>
-      <c r="T104" t="inlineStr"/>
-      <c r="U104" t="inlineStr"/>
-      <c r="V104" t="inlineStr"/>
-      <c r="W104" t="n">
+      <c r="T104" t="n">
         <v>418.333333333333</v>
       </c>
-      <c r="X104" t="n">
+      <c r="U104" t="n">
         <v>49.2024874743396</v>
       </c>
     </row>
@@ -5996,31 +4449,19 @@
           <t>FAR WAA W20-01aMgmtStandardCvAccroc</t>
         </is>
       </c>
-      <c r="B105" s="1" t="n">
+      <c r="B105" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="C105" t="inlineStr"/>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G105" t="n">
+      <c r="D105" t="n">
         <v>0.375</v>
       </c>
-      <c r="H105" t="n">
+      <c r="E105" t="n">
         <v>0.0193649167310371</v>
       </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
@@ -6034,9 +4475,6 @@
       <c r="S105" t="inlineStr"/>
       <c r="T105" t="inlineStr"/>
       <c r="U105" t="inlineStr"/>
-      <c r="V105" t="inlineStr"/>
-      <c r="W105" t="inlineStr"/>
-      <c r="X105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6044,33 +4482,21 @@
           <t>FAR WAA W20-01aMgmtStandardCvAccroc</t>
         </is>
       </c>
-      <c r="B106" s="1" t="n">
+      <c r="B106" s="3" t="n">
         <v>44132</v>
       </c>
       <c r="C106" t="inlineStr"/>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr"/>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="n">
+        <v>989.2756513938911</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0.09622689662491</v>
+      </c>
       <c r="H106" t="inlineStr"/>
-      <c r="I106" t="n">
-        <v>989.2756513938911</v>
-      </c>
-      <c r="J106" t="n">
-        <v>0.09622689662491</v>
-      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr"/>
@@ -6082,9 +4508,6 @@
       <c r="S106" t="inlineStr"/>
       <c r="T106" t="inlineStr"/>
       <c r="U106" t="inlineStr"/>
-      <c r="V106" t="inlineStr"/>
-      <c r="W106" t="inlineStr"/>
-      <c r="X106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6092,7 +4515,7 @@
           <t>FAR WAA W20-01aMgmtStandardCvAccroc</t>
         </is>
       </c>
-      <c r="B107" s="1" t="n">
+      <c r="B107" s="3" t="n">
         <v>44161</v>
       </c>
       <c r="C107" t="inlineStr">
@@ -6100,27 +4523,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G107" t="n">
+      <c r="D107" t="n">
         <v>0.11</v>
       </c>
-      <c r="H107" t="n">
+      <c r="E107" t="n">
         <v>0.0115470053837925</v>
       </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
@@ -6134,9 +4545,6 @@
       <c r="S107" t="inlineStr"/>
       <c r="T107" t="inlineStr"/>
       <c r="U107" t="inlineStr"/>
-      <c r="V107" t="inlineStr"/>
-      <c r="W107" t="inlineStr"/>
-      <c r="X107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6144,7 +4552,7 @@
           <t>FAR WAA W20-01aMgmtStandardCvAccroc</t>
         </is>
       </c>
-      <c r="B108" s="1" t="n">
+      <c r="B108" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C108" t="inlineStr">
@@ -6152,29 +4560,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr"/>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="n">
+        <v>963.510953357698</v>
+      </c>
+      <c r="G108" t="n">
+        <v>1.84030514995012</v>
+      </c>
       <c r="H108" t="inlineStr"/>
-      <c r="I108" t="n">
-        <v>963.510953357698</v>
-      </c>
-      <c r="J108" t="n">
-        <v>1.84030514995012</v>
-      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr"/>
@@ -6186,9 +4582,6 @@
       <c r="S108" t="inlineStr"/>
       <c r="T108" t="inlineStr"/>
       <c r="U108" t="inlineStr"/>
-      <c r="V108" t="inlineStr"/>
-      <c r="W108" t="inlineStr"/>
-      <c r="X108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6196,7 +4589,7 @@
           <t>FAR WAA W20-01aMgmtStandardCvAccroc</t>
         </is>
       </c>
-      <c r="B109" s="1" t="n">
+      <c r="B109" s="3" t="n">
         <v>44182</v>
       </c>
       <c r="C109" t="inlineStr">
@@ -6204,59 +4597,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
+      <c r="H109" t="n">
+        <v>78.66</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0.774413756764863</v>
+      </c>
+      <c r="J109" t="n">
+        <v>13.025</v>
+      </c>
       <c r="K109" t="n">
-        <v>78.66</v>
+        <v>0.0853912563829963</v>
       </c>
       <c r="L109" t="n">
-        <v>0.774413756764863</v>
+        <v>11.075</v>
       </c>
       <c r="M109" t="n">
-        <v>13.025</v>
+        <v>0.0629152869605894</v>
       </c>
       <c r="N109" t="n">
-        <v>0.0853912563829963</v>
+        <v>1.31997666470388</v>
       </c>
       <c r="O109" t="n">
-        <v>11.075</v>
+        <v>0.547026160657713</v>
       </c>
       <c r="P109" t="n">
-        <v>0.0629152869605894</v>
+        <v>311.601220534151</v>
       </c>
       <c r="Q109" t="n">
-        <v>1.31997666470388</v>
-      </c>
-      <c r="R109" t="n">
-        <v>0.547026160657713</v>
-      </c>
-      <c r="S109" t="n">
-        <v>311.601220534151</v>
-      </c>
-      <c r="T109" t="n">
         <v>0.216999898641518</v>
       </c>
+      <c r="R109" t="inlineStr"/>
+      <c r="S109" t="inlineStr"/>
+      <c r="T109" t="inlineStr"/>
       <c r="U109" t="inlineStr"/>
-      <c r="V109" t="inlineStr"/>
-      <c r="W109" t="inlineStr"/>
-      <c r="X109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6264,25 +4642,13 @@
           <t>FAR WAA W20-01aMgmtStandardCvAnapurna</t>
         </is>
       </c>
-      <c r="B110" s="1" t="n">
+      <c r="B110" s="3" t="n">
         <v>43997</v>
       </c>
       <c r="C110" t="inlineStr"/>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
@@ -6294,17 +4660,14 @@
       <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr"/>
       <c r="Q110" t="inlineStr"/>
-      <c r="R110" t="inlineStr"/>
-      <c r="S110" t="inlineStr"/>
+      <c r="R110" t="n">
+        <v>150</v>
+      </c>
+      <c r="S110" t="n">
+        <v>7.50856849359739</v>
+      </c>
       <c r="T110" t="inlineStr"/>
-      <c r="U110" t="n">
-        <v>150</v>
-      </c>
-      <c r="V110" t="n">
-        <v>7.50856849359739</v>
-      </c>
-      <c r="W110" t="inlineStr"/>
-      <c r="X110" t="inlineStr"/>
+      <c r="U110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6312,25 +4675,13 @@
           <t>FAR WAA W20-01aMgmtStandardCvAnapurna</t>
         </is>
       </c>
-      <c r="B111" s="1" t="n">
+      <c r="B111" s="3" t="n">
         <v>44105</v>
       </c>
       <c r="C111" t="inlineStr"/>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
@@ -6344,13 +4695,10 @@
       <c r="Q111" t="inlineStr"/>
       <c r="R111" t="inlineStr"/>
       <c r="S111" t="inlineStr"/>
-      <c r="T111" t="inlineStr"/>
-      <c r="U111" t="inlineStr"/>
-      <c r="V111" t="inlineStr"/>
-      <c r="W111" t="n">
+      <c r="T111" t="n">
         <v>441.111111111111</v>
       </c>
-      <c r="X111" t="n">
+      <c r="U111" t="n">
         <v>60.345370874726</v>
       </c>
     </row>
@@ -6360,31 +4708,19 @@
           <t>FAR WAA W20-01aMgmtStandardCvAnapurna</t>
         </is>
       </c>
-      <c r="B112" s="1" t="n">
+      <c r="B112" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="C112" t="inlineStr"/>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G112" t="n">
+      <c r="D112" t="n">
         <v>0.315</v>
       </c>
-      <c r="H112" t="n">
+      <c r="E112" t="n">
         <v>0.0225462487641145</v>
       </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
@@ -6398,9 +4734,6 @@
       <c r="S112" t="inlineStr"/>
       <c r="T112" t="inlineStr"/>
       <c r="U112" t="inlineStr"/>
-      <c r="V112" t="inlineStr"/>
-      <c r="W112" t="inlineStr"/>
-      <c r="X112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6408,33 +4741,21 @@
           <t>FAR WAA W20-01aMgmtStandardCvAnapurna</t>
         </is>
       </c>
-      <c r="B113" s="1" t="n">
+      <c r="B113" s="3" t="n">
         <v>44132</v>
       </c>
       <c r="C113" t="inlineStr"/>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="n">
+        <v>791.645271442148</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0.43894443131303</v>
+      </c>
       <c r="H113" t="inlineStr"/>
-      <c r="I113" t="n">
-        <v>791.645271442148</v>
-      </c>
-      <c r="J113" t="n">
-        <v>0.43894443131303</v>
-      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr"/>
@@ -6446,9 +4767,6 @@
       <c r="S113" t="inlineStr"/>
       <c r="T113" t="inlineStr"/>
       <c r="U113" t="inlineStr"/>
-      <c r="V113" t="inlineStr"/>
-      <c r="W113" t="inlineStr"/>
-      <c r="X113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6456,7 +4774,7 @@
           <t>FAR WAA W20-01aMgmtStandardCvAnapurna</t>
         </is>
       </c>
-      <c r="B114" s="1" t="n">
+      <c r="B114" s="3" t="n">
         <v>44161</v>
       </c>
       <c r="C114" t="inlineStr">
@@ -6464,27 +4782,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G114" t="n">
+      <c r="D114" t="n">
         <v>0.12</v>
       </c>
-      <c r="H114" t="n">
+      <c r="E114" t="n">
         <v>0.00707106781186548</v>
       </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
@@ -6498,9 +4804,6 @@
       <c r="S114" t="inlineStr"/>
       <c r="T114" t="inlineStr"/>
       <c r="U114" t="inlineStr"/>
-      <c r="V114" t="inlineStr"/>
-      <c r="W114" t="inlineStr"/>
-      <c r="X114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6508,7 +4811,7 @@
           <t>FAR WAA W20-01aMgmtStandardCvAnapurna</t>
         </is>
       </c>
-      <c r="B115" s="1" t="n">
+      <c r="B115" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C115" t="inlineStr">
@@ -6516,29 +4819,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr"/>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="n">
+        <v>793.507745043215</v>
+      </c>
+      <c r="G115" t="n">
+        <v>1.5520860323179</v>
+      </c>
       <c r="H115" t="inlineStr"/>
-      <c r="I115" t="n">
-        <v>793.507745043215</v>
-      </c>
-      <c r="J115" t="n">
-        <v>1.5520860323179</v>
-      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr"/>
@@ -6550,9 +4841,6 @@
       <c r="S115" t="inlineStr"/>
       <c r="T115" t="inlineStr"/>
       <c r="U115" t="inlineStr"/>
-      <c r="V115" t="inlineStr"/>
-      <c r="W115" t="inlineStr"/>
-      <c r="X115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6560,7 +4848,7 @@
           <t>FAR WAA W20-01aMgmtStandardCvAnapurna</t>
         </is>
       </c>
-      <c r="B116" s="1" t="n">
+      <c r="B116" s="3" t="n">
         <v>44182</v>
       </c>
       <c r="C116" t="inlineStr">
@@ -6568,59 +4856,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
+      <c r="H116" t="n">
+        <v>77.705</v>
+      </c>
+      <c r="I116" t="n">
+        <v>1.10726013203764</v>
+      </c>
+      <c r="J116" t="n">
+        <v>12.95</v>
+      </c>
       <c r="K116" t="n">
-        <v>77.705</v>
+        <v>0.104083299973307</v>
       </c>
       <c r="L116" t="n">
-        <v>1.10726013203764</v>
+        <v>12.375</v>
       </c>
       <c r="M116" t="n">
-        <v>12.95</v>
+        <v>0.137689263682152</v>
       </c>
       <c r="N116" t="n">
-        <v>0.104083299973307</v>
+        <v>2.24121196033585</v>
       </c>
       <c r="O116" t="n">
-        <v>12.375</v>
+        <v>0.283056787259634</v>
       </c>
       <c r="P116" t="n">
-        <v>0.137689263682152</v>
+        <v>246.079270783823</v>
       </c>
       <c r="Q116" t="n">
-        <v>2.24121196033585</v>
-      </c>
-      <c r="R116" t="n">
-        <v>0.283056787259634</v>
-      </c>
-      <c r="S116" t="n">
-        <v>246.079270783823</v>
-      </c>
-      <c r="T116" t="n">
         <v>0.187835056238145</v>
       </c>
+      <c r="R116" t="inlineStr"/>
+      <c r="S116" t="inlineStr"/>
+      <c r="T116" t="inlineStr"/>
       <c r="U116" t="inlineStr"/>
-      <c r="V116" t="inlineStr"/>
-      <c r="W116" t="inlineStr"/>
-      <c r="X116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6628,25 +4901,13 @@
           <t>FAR WAA W20-01aMgmtStandardCvIllabo</t>
         </is>
       </c>
-      <c r="B117" s="1" t="n">
+      <c r="B117" s="3" t="n">
         <v>43997</v>
       </c>
       <c r="C117" t="inlineStr"/>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
@@ -6658,17 +4919,14 @@
       <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr"/>
       <c r="Q117" t="inlineStr"/>
-      <c r="R117" t="inlineStr"/>
-      <c r="S117" t="inlineStr"/>
+      <c r="R117" t="n">
+        <v>112.222222222222</v>
+      </c>
+      <c r="S117" t="n">
+        <v>7.17219138186559</v>
+      </c>
       <c r="T117" t="inlineStr"/>
-      <c r="U117" t="n">
-        <v>112.222222222222</v>
-      </c>
-      <c r="V117" t="n">
-        <v>7.17219138186559</v>
-      </c>
-      <c r="W117" t="inlineStr"/>
-      <c r="X117" t="inlineStr"/>
+      <c r="U117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6676,25 +4934,13 @@
           <t>FAR WAA W20-01aMgmtStandardCvIllabo</t>
         </is>
       </c>
-      <c r="B118" s="1" t="n">
+      <c r="B118" s="3" t="n">
         <v>44105</v>
       </c>
       <c r="C118" t="inlineStr"/>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr"/>
@@ -6708,13 +4954,10 @@
       <c r="Q118" t="inlineStr"/>
       <c r="R118" t="inlineStr"/>
       <c r="S118" t="inlineStr"/>
-      <c r="T118" t="inlineStr"/>
-      <c r="U118" t="inlineStr"/>
-      <c r="V118" t="inlineStr"/>
-      <c r="W118" t="n">
+      <c r="T118" t="n">
         <v>313.888888888889</v>
       </c>
-      <c r="X118" t="n">
+      <c r="U118" t="n">
         <v>23.0828709228543</v>
       </c>
     </row>
@@ -6724,31 +4967,19 @@
           <t>FAR WAA W20-01aMgmtStandardCvIllabo</t>
         </is>
       </c>
-      <c r="B119" s="1" t="n">
+      <c r="B119" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="C119" t="inlineStr"/>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G119" t="n">
+      <c r="D119" t="n">
         <v>0.2725</v>
       </c>
-      <c r="H119" t="n">
+      <c r="E119" t="n">
         <v>0.0125</v>
       </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
@@ -6762,9 +4993,6 @@
       <c r="S119" t="inlineStr"/>
       <c r="T119" t="inlineStr"/>
       <c r="U119" t="inlineStr"/>
-      <c r="V119" t="inlineStr"/>
-      <c r="W119" t="inlineStr"/>
-      <c r="X119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6772,33 +5000,21 @@
           <t>FAR WAA W20-01aMgmtStandardCvIllabo</t>
         </is>
       </c>
-      <c r="B120" s="1" t="n">
+      <c r="B120" s="3" t="n">
         <v>44132</v>
       </c>
       <c r="C120" t="inlineStr"/>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr"/>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="n">
+        <v>983.718548261596</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.396701114146921</v>
+      </c>
       <c r="H120" t="inlineStr"/>
-      <c r="I120" t="n">
-        <v>983.718548261596</v>
-      </c>
-      <c r="J120" t="n">
-        <v>0.396701114146921</v>
-      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr"/>
@@ -6810,9 +5026,6 @@
       <c r="S120" t="inlineStr"/>
       <c r="T120" t="inlineStr"/>
       <c r="U120" t="inlineStr"/>
-      <c r="V120" t="inlineStr"/>
-      <c r="W120" t="inlineStr"/>
-      <c r="X120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6820,7 +5033,7 @@
           <t>FAR WAA W20-01aMgmtStandardCvIllabo</t>
         </is>
       </c>
-      <c r="B121" s="1" t="n">
+      <c r="B121" s="3" t="n">
         <v>44161</v>
       </c>
       <c r="C121" t="inlineStr">
@@ -6828,27 +5041,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G121" t="n">
+      <c r="D121" t="n">
         <v>0.09</v>
       </c>
-      <c r="H121" t="n">
+      <c r="E121" t="n">
         <v>0.00408248290463863</v>
       </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
@@ -6862,9 +5063,6 @@
       <c r="S121" t="inlineStr"/>
       <c r="T121" t="inlineStr"/>
       <c r="U121" t="inlineStr"/>
-      <c r="V121" t="inlineStr"/>
-      <c r="W121" t="inlineStr"/>
-      <c r="X121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6872,7 +5070,7 @@
           <t>FAR WAA W20-01aMgmtStandardCvIllabo</t>
         </is>
       </c>
-      <c r="B122" s="1" t="n">
+      <c r="B122" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C122" t="inlineStr">
@@ -6880,29 +5078,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr"/>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="n">
+        <v>1094.66914011707</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.287686934782111</v>
+      </c>
       <c r="H122" t="inlineStr"/>
-      <c r="I122" t="n">
-        <v>1094.66914011707</v>
-      </c>
-      <c r="J122" t="n">
-        <v>0.287686934782111</v>
-      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr"/>
@@ -6914,9 +5100,6 @@
       <c r="S122" t="inlineStr"/>
       <c r="T122" t="inlineStr"/>
       <c r="U122" t="inlineStr"/>
-      <c r="V122" t="inlineStr"/>
-      <c r="W122" t="inlineStr"/>
-      <c r="X122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6924,7 +5107,7 @@
           <t>FAR WAA W20-01aMgmtStandardCvIllabo</t>
         </is>
       </c>
-      <c r="B123" s="1" t="n">
+      <c r="B123" s="3" t="n">
         <v>44182</v>
       </c>
       <c r="C123" t="inlineStr">
@@ -6932,59 +5115,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
+      <c r="H123" t="n">
+        <v>71.94499999999999</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.536726187175543</v>
+      </c>
+      <c r="J123" t="n">
+        <v>12.825</v>
+      </c>
       <c r="K123" t="n">
-        <v>71.94499999999999</v>
+        <v>0.0946484724300045</v>
       </c>
       <c r="L123" t="n">
-        <v>0.536726187175543</v>
+        <v>10.5</v>
       </c>
       <c r="M123" t="n">
-        <v>12.825</v>
+        <v>0.195789002074512</v>
       </c>
       <c r="N123" t="n">
-        <v>0.0946484724300045</v>
+        <v>2.0088861627177</v>
       </c>
       <c r="O123" t="n">
-        <v>10.5</v>
+        <v>0.224483013672674</v>
       </c>
       <c r="P123" t="n">
-        <v>0.195789002074512</v>
+        <v>266.972610802219</v>
       </c>
       <c r="Q123" t="n">
-        <v>2.0088861627177</v>
-      </c>
-      <c r="R123" t="n">
-        <v>0.224483013672674</v>
-      </c>
-      <c r="S123" t="n">
-        <v>266.972610802219</v>
-      </c>
-      <c r="T123" t="n">
         <v>0.09131130409197701</v>
       </c>
+      <c r="R123" t="inlineStr"/>
+      <c r="S123" t="inlineStr"/>
+      <c r="T123" t="inlineStr"/>
       <c r="U123" t="inlineStr"/>
-      <c r="V123" t="inlineStr"/>
-      <c r="W123" t="inlineStr"/>
-      <c r="X123" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
